--- a/GunfireDungeon_Godot/excel/BuffPropBase@被动道具.xlsx
+++ b/GunfireDungeon_Godot/excel/BuffPropBase@被动道具.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28290" windowHeight="13050"/>
+    <workbookView windowWidth="24765" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/GunfireDungeon_Godot/excel/BuffPropBase@被动道具.xlsx
+++ b/GunfireDungeon_Godot/excel/BuffPropBase@被动道具.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>Id</t>
   </si>
@@ -67,6 +67,9 @@
     <t>{string:[object]}*</t>
   </si>
   <si>
+    <t>0001</t>
+  </si>
+  <si>
     <t>鞋子</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>"MoveSpeed": [30]</t>
   </si>
   <si>
+    <t>0002</t>
+  </si>
+  <si>
     <t>心之容器</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>"MaxHp":[2]</t>
   </si>
   <si>
+    <t>0003</t>
+  </si>
+  <si>
     <t>护盾</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
     <t>"MaxShield":[1]</t>
   </si>
   <si>
+    <t>0004</t>
+  </si>
+  <si>
     <t>护盾计时器</t>
   </si>
   <si>
@@ -103,6 +115,9 @@
     <t>"ShieldRecoveryTime":[2.5]</t>
   </si>
   <si>
+    <t>0005</t>
+  </si>
+  <si>
     <t>杀伤弹</t>
   </si>
   <si>
@@ -112,6 +127,9 @@
     <t>"BulletDamage":[2,0.2]</t>
   </si>
   <si>
+    <t>0006</t>
+  </si>
+  <si>
     <t>红宝石戒指</t>
   </si>
   <si>
@@ -121,6 +139,9 @@
     <t>"WoundedInvincibleTime":[2]</t>
   </si>
   <si>
+    <t>0007</t>
+  </si>
+  <si>
     <t>备用护盾</t>
   </si>
   <si>
@@ -130,6 +151,9 @@
     <t>"OffsetInjury":[0.15]</t>
   </si>
   <si>
+    <t>0008</t>
+  </si>
+  <si>
     <t>眼镜</t>
   </si>
   <si>
@@ -137,6 +161,9 @@
   </si>
   <si>
     <t>"Scattering":[0.5]</t>
+  </si>
+  <si>
+    <t>0009</t>
   </si>
   <si>
     <t>高速子弹</t>
@@ -147,6 +174,9 @@
   <si>
     <t>"BulletSpeed":[2,0.25],
 "BulletDistance":[2,0.25]</t>
+  </si>
+  <si>
+    <t>0010</t>
   </si>
   <si>
     <t>分裂子弹</t>
@@ -162,6 +192,9 @@
 "RandomBulletSpeed":[-0.05,0.05]</t>
   </si>
   <si>
+    <t>0011</t>
+  </si>
+  <si>
     <t>弹射子弹</t>
   </si>
   <si>
@@ -171,6 +204,9 @@
     <t>"BulletBounceCount":[2]</t>
   </si>
   <si>
+    <t>0012</t>
+  </si>
+  <si>
     <t>穿透子弹</t>
   </si>
   <si>
@@ -180,6 +216,9 @@
     <t>"BulletPenetration":[1]</t>
   </si>
   <si>
+    <t>0013</t>
+  </si>
+  <si>
     <t>武器背包</t>
   </si>
   <si>
@@ -187,6 +226,9 @@
   </si>
   <si>
     <t>"WeaponCapacity":[1]</t>
+  </si>
+  <si>
+    <t>0014</t>
   </si>
   <si>
     <t>道具背包</t>
@@ -1509,166 +1551,200 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="33" customHeight="1" spans="2:4">
+    <row r="4" ht="33" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:4">
-      <c r="A5" s="6"/>
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:4">
-      <c r="A6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:4">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:4">
-      <c r="A8" s="6"/>
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:4">
-      <c r="A9" s="6"/>
+      <c r="A9" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="B9" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" spans="1:4">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:4">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" spans="1:4">
-      <c r="A12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" ht="87" customHeight="1" spans="2:4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="87" customHeight="1" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="2:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="2:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" ht="29" customHeight="1" spans="2:4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" ht="29" customHeight="1" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="2:4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1"/>
@@ -1750,92 +1826,92 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="1" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="1" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
